--- a/artfynd/A 46329-2022 artfynd.xlsx
+++ b/artfynd/A 46329-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46329-2022 artfynd.xlsx
+++ b/artfynd/A 46329-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY106"/>
+  <dimension ref="A1:AZ106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110552498</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790176</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551460</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387056</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110552264</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387105</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505052</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387054</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790179</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1785,6 +1840,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387104</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790173</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790175</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790178</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2218,6 +2293,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505021</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2332,6 +2412,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790149</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2446,6 +2531,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790150</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790151</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2674,6 +2769,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790152</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2772,6 +2872,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110551362</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2869,6 +2974,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387066</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2966,6 +3076,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387067</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3063,6 +3178,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387069</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3160,6 +3280,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387070</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3257,6 +3382,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387071</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3354,6 +3484,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505023</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3451,6 +3586,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505024</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3548,6 +3688,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3645,6 +3790,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505026</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3742,6 +3892,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505027</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3839,6 +3994,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505028</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505029</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4044,6 +4209,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578520</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4152,6 +4322,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578582</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4260,6 +4435,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578662</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4368,6 +4548,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578792</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4476,6 +4661,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578830</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4584,6 +4774,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578841</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4692,6 +4887,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578865</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4800,6 +5000,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578960</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4908,6 +5113,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578990</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5006,6 +5216,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111579233</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5104,6 +5319,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111579490</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5202,6 +5422,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111579503</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5300,6 +5525,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111579563</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5397,6 +5627,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387063</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5511,6 +5746,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790148</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5608,6 +5848,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505017</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5716,6 +5961,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578583</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5813,6 +6063,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505049</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5910,6 +6165,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505050</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6017,6 +6277,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110557695</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6125,6 +6390,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578950</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6223,6 +6493,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110556717</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6321,6 +6596,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110556780</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6419,6 +6699,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111506378</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6525,6 +6810,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790174</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6631,6 +6921,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790177</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6737,6 +7032,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387073</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6843,6 +7143,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387075</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6949,6 +7254,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387076</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7055,6 +7365,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387077</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7161,6 +7476,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387078</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7267,6 +7587,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387079</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7373,6 +7698,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387080</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7479,6 +7809,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387081</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7585,6 +7920,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387082</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7691,6 +8031,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387083</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7797,6 +8142,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387084</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7903,6 +8253,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387085</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8009,6 +8364,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387086</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8115,6 +8475,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387087</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8221,6 +8586,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387088</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8327,6 +8697,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387089</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8433,6 +8808,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387090</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8539,6 +8919,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387091</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8645,6 +9030,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387092</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8751,6 +9141,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387093</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8857,6 +9252,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387094</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8963,6 +9363,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387096</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9069,6 +9474,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387097</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9175,6 +9585,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387099</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9281,6 +9696,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505030</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9387,6 +9807,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505031</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9493,6 +9918,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505032</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9599,6 +10029,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505033</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9705,6 +10140,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505034</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9811,6 +10251,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505035</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9917,6 +10362,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505036</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10023,6 +10473,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505037</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10129,6 +10584,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505038</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10235,6 +10695,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505040</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10341,6 +10806,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505041</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10447,6 +10917,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505042</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10553,6 +11028,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111505043</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10660,6 +11140,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111506427</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10758,6 +11243,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111579081</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10856,6 +11346,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111579646</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10964,6 +11459,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110556614</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11061,6 +11561,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387100</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11158,6 +11663,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387101</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11255,6 +11765,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111387102</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11363,6 +11878,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111578704</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11461,6 +11981,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110557132</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11559,8 +12084,120 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111506366</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>